--- a/output/Bo_Bao_Cao_Tai_Chinh_Q1_Q2_2026.xlsx
+++ b/output/Bo_Bao_Cao_Tai_Chinh_Q1_Q2_2026.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,16 +196,25 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -622,7 +631,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -636,7 +645,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo quản trị phân tích biến động kết quả kinh doanh và tình hình tài chính Q1 &amp; Q2/2026</t>
+          <t>Hệ thống phân tích báo cáo tài chính đa kỳ - Năm 2026 (Đơn vị tính: VNĐ)</t>
         </is>
       </c>
     </row>
@@ -644,7 +653,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1. CÁC CHỈ SỐ TÀI CHÍNH CHỦ YẾU</t>
+          <t>1. CÁC CHỈ SỐ TÀI CHÍNH CHỦ YẾU QUA CÁC KỲ</t>
         </is>
       </c>
     </row>
@@ -671,17 +680,17 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Lũy kế 6T/2026</t>
+          <t>Tổng các kỳ</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Tăng trưởng Q2/Q1</t>
+          <t>Tăng trưởng kỳ cuối</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Đánh giá chuyên sâu</t>
+          <t>Đánh giá tổng quan</t>
         </is>
       </c>
     </row>
@@ -710,7 +719,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Tăng trưởng +11.0%</t>
+          <t>Tăng trưởng doanh thu tích cực</t>
         </is>
       </c>
     </row>
@@ -739,7 +748,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Tăng trưởng +7.8%</t>
+          <t>Biên lợi nhuận gộp ổn định</t>
         </is>
       </c>
     </row>
@@ -768,7 +777,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Biên gộp duy trì cao (~77-80%)</t>
+          <t>Biên gộp duy trì ở mức rất cao</t>
         </is>
       </c>
     </row>
@@ -797,7 +806,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Tăng trưởng vượt bậc +39.7%</t>
+          <t>Hiệu quả kinh doanh vượt bậc</t>
         </is>
       </c>
     </row>
@@ -818,7 +827,7 @@
       <c r="D11" s="16" t="n">
         <v>1086773307</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="7" t="n">
         <v>1865460838</v>
       </c>
       <c r="F11" s="8" t="n">
@@ -826,7 +835,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Trích nộp đúng quy định 20%</t>
+          <t>Tuân thủ nghĩa vụ thuế</t>
         </is>
       </c>
     </row>
@@ -855,7 +864,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Tăng trưởng xuất sắc +39.8%</t>
+          <t>Tăng trưởng lợi nhuận mạnh</t>
         </is>
       </c>
     </row>
@@ -884,7 +893,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Biên ròng tăng mạnh từ 25.9% lên 32.6%</t>
+          <t>Tỷ suất sinh lời ròng rất ấn tượng</t>
         </is>
       </c>
     </row>
@@ -905,7 +914,7 @@
       <c r="D14" s="17" t="n">
         <v>303330808584</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="12" t="n">
         <v>303330808584</v>
       </c>
       <c r="F14" s="13" t="n">
@@ -913,7 +922,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Tài sản tăng trưởng +38.5%</t>
+          <t>Quy mô tài sản liên tục mở rộng</t>
         </is>
       </c>
     </row>
@@ -934,7 +943,7 @@
       <c r="D15" s="16" t="n">
         <v>84528791474</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="7" t="n">
         <v>84528791474</v>
       </c>
       <c r="F15" s="8" t="n">
@@ -942,7 +951,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Tăng trưởng do tích lũy lợi nhuận</t>
+          <t>Gia tăng từ lợi nhuận giữ lại</t>
         </is>
       </c>
     </row>
@@ -963,15 +972,15 @@
       <c r="D16" s="18" t="n">
         <v>1.386123254766552</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>1.386123254766552</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <v>-0.1913499760332835</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Thanh toán an toàn (&gt;1.38 lần)</t>
+          <t>Thanh toán an toàn (&gt;1.35 lần)</t>
         </is>
       </c>
     </row>
@@ -986,21 +995,21 @@
           <t>Lần</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <v>0.8766677593543658</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="21" t="n">
         <v>0.8844054441496094</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="22" t="n">
         <v>0.8844054441496094</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="23" t="n">
         <v>0.007737684795243616</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Thanh khoản tiền mặt cực cao (~0.88 lần)</t>
+          <t>Dồi dào thanh khoản tiền mặt</t>
         </is>
       </c>
     </row>
@@ -1015,13 +1024,13 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="24" t="n">
         <v>0.6337805235799773</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="24" t="n">
         <v>0.7213313350246392</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="25" t="n">
         <v>0.7213313350246392</v>
       </c>
       <c r="F18" s="13" t="n">
@@ -1029,7 +1038,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>Không có nợ vay, hoàn toàn là nợ hoạt động</t>
+          <t>Không sử dụng nợ vay ngân hàng</t>
         </is>
       </c>
     </row>
@@ -1051,10 +1060,10 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1073,9 +1082,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>Tại các thời điểm: 01/01/2026, 31/03/2026 và 30/06/2026 (Đơn vị tính: VNĐ)</t>
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Đơn vị tính: VNĐ - So sánh số liệu qua 2 kỳ kế toán</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1112,17 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Cuối Quý 1 (31/03/2026)</t>
+          <t>Cuối Quý 1/2026</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Cuối Quý 2 (30/06/2026)</t>
+          <t>Cuối Quý 2/2026</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Biến động Q2 vs Q1</t>
+          <t>Biến động lũy kế</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1123,63 +1132,63 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>A. TÀI SẢN NGẮN HẠN</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr"/>
-      <c r="D7" s="26" t="n">
+      <c r="C7" s="28" t="inlineStr"/>
+      <c r="D7" s="29" t="n">
         <v>440297325428</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="29" t="n">
         <v>218935374375</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="29" t="n">
         <v>303286564106</v>
       </c>
-      <c r="G7" s="26" t="n">
-        <v>84351189731</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0.3852789434864025</v>
+      <c r="G7" s="29" t="n">
+        <v>-137010761322</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>-0.3111778187360459</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>I. Tiền và các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>V.01</t>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="29" t="n">
         <v>349015806508</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="29" t="n">
         <v>121671531630</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="29" t="n">
         <v>193509695123</v>
       </c>
-      <c r="G8" s="26" t="n">
-        <v>71838163493</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0.5904270500305528</v>
+      <c r="G8" s="29" t="n">
+        <v>-155506111385</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>-0.445556070771928</v>
       </c>
     </row>
     <row r="9">
@@ -1188,26 +1197,26 @@
           <t xml:space="preserve">   1. Tiền (TK 111, 112)</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr"/>
-      <c r="D9" s="29" t="n">
+      <c r="C9" s="31" t="inlineStr"/>
+      <c r="D9" s="32" t="n">
         <v>340015806508</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="32" t="n">
         <v>121671531630</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="32" t="n">
         <v>193509695123</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>71838163493</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>0.5904270500305528</v>
+      <c r="G9" s="32" t="n">
+        <v>-146506111385</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>-0.4308802960945669</v>
       </c>
     </row>
     <row r="10">
@@ -1216,58 +1225,58 @@
           <t xml:space="preserve">   2. Các khoản tương đương tiền (TK 1281-kỳ hạn &lt;=3T)</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr"/>
-      <c r="D10" s="29" t="n">
+      <c r="C10" s="31" t="inlineStr"/>
+      <c r="D10" s="32" t="n">
         <v>9000000000</v>
       </c>
-      <c r="E10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>0</v>
+      <c r="E10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>-9000000000</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>II. Đầu tư tài chính ngắn hạn</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>V.02</t>
         </is>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="29" t="n">
         <v>49000000000</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="29" t="n">
         <v>65000000000</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <v>66000000000</v>
       </c>
-      <c r="G11" s="26" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>0.01538461538461539</v>
+      <c r="G11" s="29" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>0.3469387755102041</v>
       </c>
     </row>
     <row r="12">
@@ -1276,58 +1285,58 @@
           <t xml:space="preserve">   1. Đầu tư nắm giữ đến ngày đáo hạn (TK 1281-kỳ hạn 6-12T)</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr"/>
-      <c r="D12" s="29" t="n">
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="32" t="n">
         <v>49000000000</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="32" t="n">
         <v>65000000000</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="32" t="n">
         <v>66000000000</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="H12" s="30" t="n">
-        <v>0.01538461538461539</v>
+      <c r="G12" s="32" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>0.3469387755102041</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>III. Các khoản phải thu ngắn hạn</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>V.03</t>
         </is>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="29" t="n">
         <v>42046942920</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="29" t="n">
         <v>32205198745</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="29" t="n">
         <v>43776868983</v>
       </c>
-      <c r="G13" s="26" t="n">
-        <v>11571670238</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>0.3593106296167961</v>
+      <c r="G13" s="29" t="n">
+        <v>1729926063</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0.04114273102544978</v>
       </c>
     </row>
     <row r="14">
@@ -1336,89 +1345,89 @@
           <t xml:space="preserve">   1. Phải thu ngắn hạn khác (TK 138, 141)</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr"/>
-      <c r="D14" s="29" t="n">
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="32" t="n">
         <v>42046942920</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="32" t="n">
         <v>32205198745</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="32" t="n">
         <v>43776868983</v>
       </c>
-      <c r="G14" s="29" t="n">
-        <v>11571670238</v>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>0.3593106296167961</v>
+      <c r="G14" s="32" t="n">
+        <v>1729926063</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>0.04114273102544978</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>IV. Hàng tồn kho</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>V.04</t>
         </is>
       </c>
-      <c r="D15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="27" t="n">
+      <c r="D15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>V. Tài sản ngắn hạn khác</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>V.05</t>
         </is>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="29" t="n">
         <v>234576000</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="29" t="n">
         <v>58644000</v>
       </c>
-      <c r="F16" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-58644000</v>
-      </c>
-      <c r="H16" s="27" t="n">
+      <c r="F16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>-234576000</v>
+      </c>
+      <c r="H16" s="30" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1428,25 +1437,25 @@
           <t xml:space="preserve">   1. Chi phí trả trước ngắn hạn (TK 2421)</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr"/>
-      <c r="D17" s="29" t="n">
+      <c r="C17" s="31" t="inlineStr"/>
+      <c r="D17" s="32" t="n">
         <v>234576000</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="32" t="n">
         <v>58644000</v>
       </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>-58644000</v>
-      </c>
-      <c r="H17" s="30" t="n">
+      <c r="F17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>-234576000</v>
+      </c>
+      <c r="H17" s="33" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1456,86 +1465,86 @@
           <t xml:space="preserve">   2. Thuế giá trị gia tăng được khấu trừ (TK 133)</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr"/>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="30" t="n">
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>B. TÀI SẢN DÀI HẠN</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr"/>
-      <c r="D19" s="26" t="n">
+      <c r="C19" s="28" t="inlineStr"/>
+      <c r="D19" s="29" t="n">
         <v>55695988</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="29" t="n">
         <v>49970233</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="29" t="n">
         <v>44244478</v>
       </c>
-      <c r="G19" s="26" t="n">
-        <v>-5725755</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.1145833160313661</v>
+      <c r="G19" s="29" t="n">
+        <v>-11451510</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>-0.2056074487806913</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>II. Tài sản cố định</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>V.08</t>
         </is>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="29" t="n">
         <v>40695988</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="29" t="n">
         <v>34970233</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="29" t="n">
         <v>29244478</v>
       </c>
-      <c r="G20" s="26" t="n">
-        <v>-5725755</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-0.1637322519412439</v>
+      <c r="G20" s="29" t="n">
+        <v>-11451510</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>-0.2813916202255613</v>
       </c>
     </row>
     <row r="21">
@@ -1544,26 +1553,26 @@
           <t xml:space="preserve">   1. Tài sản cố định hữu hình</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr"/>
-      <c r="D21" s="29" t="n">
+      <c r="C21" s="31" t="inlineStr"/>
+      <c r="D21" s="32" t="n">
         <v>40695988</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="32" t="n">
         <v>34970233</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="32" t="n">
         <v>29244478</v>
       </c>
-      <c r="G21" s="29" t="n">
-        <v>-5725755</v>
-      </c>
-      <c r="H21" s="30" t="n">
-        <v>-0.1637322519412439</v>
+      <c r="G21" s="32" t="n">
+        <v>-11451510</v>
+      </c>
+      <c r="H21" s="33" t="n">
+        <v>-0.2813916202255613</v>
       </c>
     </row>
     <row r="22">
@@ -1572,26 +1581,26 @@
           <t xml:space="preserve">      - Nguyên giá (TK 211)</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>222</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr"/>
-      <c r="D22" s="29" t="n">
+      <c r="C22" s="31" t="inlineStr"/>
+      <c r="D22" s="32" t="n">
         <v>2778069546</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="32" t="n">
         <v>2675231364</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="32" t="n">
         <v>2675231364</v>
       </c>
-      <c r="G22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>0</v>
+      <c r="G22" s="32" t="n">
+        <v>-102838182</v>
+      </c>
+      <c r="H22" s="33" t="n">
+        <v>-0.03701785729161152</v>
       </c>
     </row>
     <row r="23">
@@ -1600,57 +1609,57 @@
           <t xml:space="preserve">      - Giá trị hao mòn lũy kế (TK 214)</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr"/>
-      <c r="D23" s="29" t="n">
+      <c r="C23" s="31" t="inlineStr"/>
+      <c r="D23" s="32" t="n">
         <v>-2737373558</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="32" t="n">
         <v>-2640261131</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="32" t="n">
         <v>-2645986886</v>
       </c>
-      <c r="G23" s="29" t="n">
-        <v>-5725755</v>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>-0.002168632084445135</v>
+      <c r="G23" s="32" t="n">
+        <v>91386672</v>
+      </c>
+      <c r="H23" s="33" t="n">
+        <v>0.03338480118393838</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>VI. Tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>V.12</t>
         </is>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="G24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="27" t="n">
+      <c r="G24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1660,114 +1669,114 @@
           <t xml:space="preserve">   1. Tài sản dài hạn khác (Ký quỹ dài hạn TK 244)</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr"/>
-      <c r="D25" s="29" t="n">
+      <c r="C25" s="31" t="inlineStr"/>
+      <c r="D25" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="G25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="30" t="n">
+      <c r="G25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TÀI SẢN (270 = 100 + 200)</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr"/>
-      <c r="D26" s="33" t="n">
+      <c r="C26" s="35" t="inlineStr"/>
+      <c r="D26" s="36" t="n">
         <v>440353021416</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="36" t="n">
         <v>218985344608</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="36" t="n">
         <v>303330808584</v>
       </c>
-      <c r="G26" s="33" t="n">
-        <v>84345463976</v>
-      </c>
-      <c r="H26" s="34" t="n">
-        <v>0.3851648799922416</v>
+      <c r="G26" s="36" t="n">
+        <v>-137022212832</v>
+      </c>
+      <c r="H26" s="37" t="n">
+        <v>-0.3111644661626055</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>C. NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr"/>
-      <c r="D27" s="26" t="n">
+      <c r="C27" s="28" t="inlineStr"/>
+      <c r="D27" s="29" t="n">
         <v>363256073292</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="29" t="n">
         <v>138788646362</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="29" t="n">
         <v>218802017110</v>
       </c>
-      <c r="G27" s="26" t="n">
-        <v>80013370748</v>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>0.5765123649905953</v>
+      <c r="G27" s="29" t="n">
+        <v>-144454056182</v>
+      </c>
+      <c r="H27" s="30" t="n">
+        <v>-0.3976645314499173</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>I. Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>V.15</t>
         </is>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="29" t="n">
         <v>363256073292</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="29" t="n">
         <v>138788646362</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="29" t="n">
         <v>218802017110</v>
       </c>
-      <c r="G28" s="26" t="n">
-        <v>80013370748</v>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>0.5765123649905953</v>
+      <c r="G28" s="29" t="n">
+        <v>-144454056182</v>
+      </c>
+      <c r="H28" s="30" t="n">
+        <v>-0.3976645314499173</v>
       </c>
     </row>
     <row r="29">
@@ -1776,26 +1785,26 @@
           <t xml:space="preserve">   1. Thuế và các khoản phải nộp Nhà nước (TK 333)</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>313</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr"/>
-      <c r="D29" s="29" t="n">
+      <c r="C29" s="31" t="inlineStr"/>
+      <c r="D29" s="32" t="n">
         <v>2104207557</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="32" t="n">
         <v>1122238566</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="32" t="n">
         <v>1803533628</v>
       </c>
-      <c r="G29" s="29" t="n">
-        <v>681295062</v>
-      </c>
-      <c r="H29" s="30" t="n">
-        <v>0.6070857682500995</v>
+      <c r="G29" s="32" t="n">
+        <v>-300673929</v>
+      </c>
+      <c r="H29" s="33" t="n">
+        <v>-0.1428917636949633</v>
       </c>
     </row>
     <row r="30">
@@ -1804,26 +1813,26 @@
           <t xml:space="preserve">   2. Phải trả người lao động (TK 334)</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr"/>
-      <c r="D30" s="29" t="n">
+      <c r="C30" s="31" t="inlineStr"/>
+      <c r="D30" s="32" t="n">
         <v>5432454882</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="32" t="n">
         <v>2217911529</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="32" t="n">
         <v>2680025652</v>
       </c>
-      <c r="G30" s="29" t="n">
-        <v>462114123</v>
-      </c>
-      <c r="H30" s="30" t="n">
-        <v>0.2083555258889679</v>
+      <c r="G30" s="32" t="n">
+        <v>-2752429230</v>
+      </c>
+      <c r="H30" s="33" t="n">
+        <v>-0.5066639833714868</v>
       </c>
     </row>
     <row r="31">
@@ -1832,26 +1841,26 @@
           <t xml:space="preserve">   3. Chi phí phải trả ngắn hạn (TK 335)</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>315</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr"/>
-      <c r="D31" s="29" t="n">
+      <c r="C31" s="31" t="inlineStr"/>
+      <c r="D31" s="32" t="n">
         <v>1552685577</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="32" t="n">
         <v>2110882847</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="32" t="n">
         <v>3174019640</v>
       </c>
-      <c r="G31" s="29" t="n">
-        <v>1063136793</v>
-      </c>
-      <c r="H31" s="30" t="n">
-        <v>0.5036455692038697</v>
+      <c r="G31" s="32" t="n">
+        <v>1621334063</v>
+      </c>
+      <c r="H31" s="33" t="n">
+        <v>1.044212741469936</v>
       </c>
     </row>
     <row r="32">
@@ -1860,26 +1869,26 @@
           <t xml:space="preserve">   4. Phải trả ngắn hạn khác (TK 338)</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>319</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr"/>
-      <c r="D32" s="29" t="n">
+      <c r="C32" s="31" t="inlineStr"/>
+      <c r="D32" s="32" t="n">
         <v>353628589247</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="32" t="n">
         <v>133219477391</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="32" t="n">
         <v>211027802161</v>
       </c>
-      <c r="G32" s="29" t="n">
-        <v>77808324770</v>
-      </c>
-      <c r="H32" s="30" t="n">
-        <v>0.5840611770426939</v>
+      <c r="G32" s="32" t="n">
+        <v>-142600787086</v>
+      </c>
+      <c r="H32" s="33" t="n">
+        <v>-0.4032501653490386</v>
       </c>
     </row>
     <row r="33">
@@ -1888,86 +1897,86 @@
           <t xml:space="preserve">   5. Quỹ khen thưởng, phúc lợi (TK 353)</t>
         </is>
       </c>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>322</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr"/>
-      <c r="D33" s="29" t="n">
+      <c r="C33" s="31" t="inlineStr"/>
+      <c r="D33" s="32" t="n">
         <v>538136029</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="32" t="n">
         <v>118136029</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="32" t="n">
         <v>116636029</v>
       </c>
-      <c r="G33" s="29" t="n">
-        <v>-1500000</v>
-      </c>
-      <c r="H33" s="30" t="n">
-        <v>-0.01269722719391558</v>
+      <c r="G33" s="32" t="n">
+        <v>-421500000</v>
+      </c>
+      <c r="H33" s="33" t="n">
+        <v>-0.7832592082400787</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>D. VỐN CHỦ SỞ HỮU</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr"/>
-      <c r="D34" s="26" t="n">
+      <c r="C34" s="28" t="inlineStr"/>
+      <c r="D34" s="29" t="n">
         <v>77096948124</v>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="29" t="n">
         <v>80196698246</v>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="29" t="n">
         <v>84528791474</v>
       </c>
-      <c r="G34" s="26" t="n">
-        <v>4332093228</v>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>0.05401834891894784</v>
+      <c r="G34" s="29" t="n">
+        <v>7431843350</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <v>0.09639607702819684</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>I. Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>V.22</t>
         </is>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="29" t="n">
         <v>77096948124</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="29" t="n">
         <v>80196698246</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="29" t="n">
         <v>84528791474</v>
       </c>
-      <c r="G35" s="26" t="n">
-        <v>4332093228</v>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>0.05401834891894784</v>
+      <c r="G35" s="29" t="n">
+        <v>7431843350</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>0.09639607702819684</v>
       </c>
     </row>
     <row r="36">
@@ -1976,25 +1985,25 @@
           <t xml:space="preserve">   1. Vốn góp của chủ sở hữu (TK 4111)</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr"/>
-      <c r="D36" s="29" t="n">
+      <c r="C36" s="31" t="inlineStr"/>
+      <c r="D36" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="G36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="30" t="n">
+      <c r="G36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2004,25 +2013,25 @@
           <t xml:space="preserve">   2. Chênh lệch tỷ giá hối đoái (TK 413)</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>415</t>
         </is>
       </c>
-      <c r="C37" s="28" t="inlineStr"/>
-      <c r="D37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="30" t="n">
+      <c r="C37" s="31" t="inlineStr"/>
+      <c r="D37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2032,25 +2041,25 @@
           <t xml:space="preserve">   3. Quỹ đầu tư phát triển (TK 414)</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>418</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr"/>
-      <c r="D38" s="29" t="n">
+      <c r="C38" s="31" t="inlineStr"/>
+      <c r="D38" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="G38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="30" t="n">
+      <c r="G38" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2060,54 +2069,54 @@
           <t xml:space="preserve">   4. Quỹ khác thuộc vốn chủ sở hữu (TK 418)</t>
         </is>
       </c>
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="C39" s="28" t="inlineStr"/>
-      <c r="D39" s="29" t="n">
+      <c r="C39" s="31" t="inlineStr"/>
+      <c r="D39" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="G39" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="30" t="n">
+      <c r="G39" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">   5. Lợi nhuận sau thuế chưa phân phối (TK 421)</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>421</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr"/>
-      <c r="D40" s="26" t="n">
+      <c r="C40" s="28" t="inlineStr"/>
+      <c r="D40" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="E40" s="26" t="n">
+      <c r="E40" s="29" t="n">
         <v>21067184167</v>
       </c>
-      <c r="F40" s="26" t="n">
+      <c r="F40" s="29" t="n">
         <v>25399277395</v>
       </c>
-      <c r="G40" s="26" t="n">
-        <v>4332093228</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>0.2056322854378358</v>
+      <c r="G40" s="29" t="n">
+        <v>7431843350</v>
+      </c>
+      <c r="H40" s="30" t="n">
+        <v>0.4136285310070829</v>
       </c>
     </row>
     <row r="41">
@@ -2116,25 +2125,25 @@
           <t xml:space="preserve">      - LNST chưa phân phối lũy kế năm trước (TK 4211)</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>421a</t>
         </is>
       </c>
-      <c r="C41" s="28" t="inlineStr"/>
-      <c r="D41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="29" t="n">
+      <c r="C41" s="31" t="inlineStr"/>
+      <c r="D41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="G41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="30" t="n">
+      <c r="G41" s="32" t="n">
+        <v>17967434045</v>
+      </c>
+      <c r="H41" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2144,81 +2153,81 @@
           <t xml:space="preserve">      - LNST chưa phân phối năm nay (TK 4212 + LN trong kỳ)</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>421b</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr"/>
-      <c r="D42" s="29" t="n">
+      <c r="C42" s="31" t="inlineStr"/>
+      <c r="D42" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="32" t="n">
         <v>3099750122</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="32" t="n">
         <v>7431843350</v>
       </c>
-      <c r="G42" s="29" t="n">
-        <v>4332093228</v>
-      </c>
-      <c r="H42" s="30" t="n">
-        <v>1.397562080005622</v>
+      <c r="G42" s="32" t="n">
+        <v>-10535590695</v>
+      </c>
+      <c r="H42" s="33" t="n">
+        <v>-0.586371468992917</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>TỔNG CỘNG NGUỒN VỐN (440 = 300 + 400)</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr"/>
-      <c r="D43" s="33" t="n">
+      <c r="C43" s="35" t="inlineStr"/>
+      <c r="D43" s="36" t="n">
         <v>440353021416</v>
       </c>
-      <c r="E43" s="33" t="n">
+      <c r="E43" s="36" t="n">
         <v>218985344608</v>
       </c>
-      <c r="F43" s="33" t="n">
+      <c r="F43" s="36" t="n">
         <v>303330808584</v>
       </c>
-      <c r="G43" s="33" t="n">
-        <v>84345463976</v>
-      </c>
-      <c r="H43" s="34" t="n">
-        <v>0.3851648799922416</v>
+      <c r="G43" s="36" t="n">
+        <v>-137022212832</v>
+      </c>
+      <c r="H43" s="37" t="n">
+        <v>-0.3111644661626055</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>KIỂM TRA CÂN ĐỐI (TÀI SẢN - NGUỒN VỐN)</t>
         </is>
       </c>
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>CHK</t>
         </is>
       </c>
-      <c r="C44" s="36" t="inlineStr"/>
-      <c r="D44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="38" t="n">
+      <c r="C44" s="39" t="inlineStr"/>
+      <c r="D44" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2233,17 +2242,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -2262,9 +2270,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>Cho giai đoạn: Quý 1, Quý 2 và Lũy kế 6 tháng năm 2026 (Đơn vị tính: VNĐ)</t>
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Đơn vị tính: VNĐ - Phân tích doanh thu, chi phí và lợi nhuận qua 2 kỳ</t>
         </is>
       </c>
     </row>
@@ -2297,17 +2305,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Lũy kế 6T/2026</t>
+          <t>Tổng các kỳ</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Tăng/Giảm (Q2-Q1)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Tăng trưởng (%)</t>
+          <t>Tăng trưởng kỳ cuối (%)</t>
         </is>
       </c>
     </row>
@@ -2317,29 +2320,26 @@
           <t>1. Doanh thu bán hàng và cung cấp dịch vụ</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>VI.25</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="32" t="n">
         <v>11955764348</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="32" t="n">
         <v>13273671288</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="32" t="n">
         <v>25229435636</v>
       </c>
-      <c r="G7" s="29" t="n">
-        <v>1317906940</v>
-      </c>
-      <c r="H7" s="30" t="n">
+      <c r="G7" s="33" t="n">
         <v>0.1102319267626301</v>
       </c>
     </row>
@@ -2349,61 +2349,55 @@
           <t>2. Các khoản giảm trừ doanh thu</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>VI.26</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="30" t="n">
+      <c r="D8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>3. Doanh thu thuần về bán hàng và CCDV (10 = 01 - 02)</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>VI.27</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="29" t="n">
         <v>11955764348</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="29" t="n">
         <v>13273671288</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="29" t="n">
         <v>25229435636</v>
       </c>
-      <c r="G9" s="26" t="n">
-        <v>1317906940</v>
-      </c>
-      <c r="H9" s="27" t="n">
+      <c r="G9" s="30" t="n">
         <v>0.1102319267626301</v>
       </c>
     </row>
@@ -2413,57 +2407,51 @@
           <t>4. Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>VI.28</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="32" t="n">
         <v>2419176930</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="32" t="n">
         <v>2991439196</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="32" t="n">
         <v>5410616126</v>
       </c>
-      <c r="G10" s="29" t="n">
-        <v>572262266</v>
-      </c>
-      <c r="H10" s="30" t="n">
+      <c r="G10" s="33" t="n">
         <v>0.23655246497411</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>5. Lợi nhuận gộp về bán hàng và CCDV (20 = 10 - 11)</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr"/>
-      <c r="D11" s="26" t="n">
+      <c r="C11" s="28" t="inlineStr"/>
+      <c r="D11" s="29" t="n">
         <v>9536587418</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="29" t="n">
         <v>10282232092</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <v>19818819510</v>
       </c>
-      <c r="G11" s="26" t="n">
-        <v>745644674</v>
-      </c>
-      <c r="H11" s="27" t="n">
+      <c r="G11" s="30" t="n">
         <v>0.07818778786556498</v>
       </c>
     </row>
@@ -2473,29 +2461,26 @@
           <t>6. Doanh thu hoạt động tài chính</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>VI.29</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="32" t="n">
         <v>983066826</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="32" t="n">
         <v>1428466738</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="32" t="n">
         <v>2411533564</v>
       </c>
-      <c r="G12" s="29" t="n">
-        <v>445399912</v>
-      </c>
-      <c r="H12" s="30" t="n">
+      <c r="G12" s="33" t="n">
         <v>0.4530718565820062</v>
       </c>
     </row>
@@ -2505,29 +2490,26 @@
           <t>7. Chi phí tài chính</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>VI.30</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="32" t="n">
         <v>60403</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="32" t="n">
         <v>15799</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="32" t="n">
         <v>76202</v>
       </c>
-      <c r="G13" s="29" t="n">
-        <v>-44604</v>
-      </c>
-      <c r="H13" s="30" t="n">
+      <c r="G13" s="33" t="n">
         <v>-0.7384401437014718</v>
       </c>
     </row>
@@ -2537,25 +2519,22 @@
           <t xml:space="preserve">   - Trong đó: Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr"/>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="30" t="n">
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2565,29 +2544,26 @@
           <t>8. Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>VI.31</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="30" t="n">
+      <c r="D15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2597,57 +2573,51 @@
           <t>9. Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>VI.32</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="32" t="n">
         <v>6641156188</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="32" t="n">
         <v>6291816496</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="32" t="n">
         <v>12932972684</v>
       </c>
-      <c r="G16" s="29" t="n">
-        <v>-349339692</v>
-      </c>
-      <c r="H16" s="30" t="n">
+      <c r="G16" s="33" t="n">
         <v>-0.05260224004838598</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>10. Lợi nhuận thuần từ HĐKD {30 = 20 + (21 - 22) - 25 - 26}</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr"/>
-      <c r="D17" s="26" t="n">
+      <c r="C17" s="28" t="inlineStr"/>
+      <c r="D17" s="29" t="n">
         <v>3878437653</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="29" t="n">
         <v>5418866535</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="29" t="n">
         <v>9297304188</v>
       </c>
-      <c r="G17" s="26" t="n">
-        <v>1540428882</v>
-      </c>
-      <c r="H17" s="27" t="n">
+      <c r="G17" s="30" t="n">
         <v>0.3971776833407305</v>
       </c>
     </row>
@@ -2657,25 +2627,22 @@
           <t>11. Thu nhập khác</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr"/>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="30" t="n">
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2685,25 +2652,22 @@
           <t>12. Chi phí khác</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr"/>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="30" t="n">
+      <c r="C19" s="31" t="inlineStr"/>
+      <c r="D19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2713,53 +2677,47 @@
           <t>13. Lợi nhuận khác (40 = 31 - 32)</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr"/>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="30" t="n">
+      <c r="C20" s="31" t="inlineStr"/>
+      <c r="D20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>14. Tổng lợi nhuận kế toán trước thuế (50 = 30 + 40)</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr"/>
-      <c r="D21" s="26" t="n">
+      <c r="C21" s="28" t="inlineStr"/>
+      <c r="D21" s="29" t="n">
         <v>3878437653</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="29" t="n">
         <v>5418866535</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="29" t="n">
         <v>9297304188</v>
       </c>
-      <c r="G21" s="26" t="n">
-        <v>1540428882</v>
-      </c>
-      <c r="H21" s="27" t="n">
+      <c r="G21" s="30" t="n">
         <v>0.3971776833407305</v>
       </c>
     </row>
@@ -2769,29 +2727,26 @@
           <t>15. Chi phí thuế TNDN hiện hành (TK 8211)</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>VI.35</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="32" t="n">
         <v>778687531</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="32" t="n">
         <v>1086773307</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="32" t="n">
         <v>1865460838</v>
       </c>
-      <c r="G22" s="29" t="n">
-        <v>308085776</v>
-      </c>
-      <c r="H22" s="30" t="n">
+      <c r="G22" s="33" t="n">
         <v>0.3956475013852508</v>
       </c>
     </row>
@@ -2801,53 +2756,47 @@
           <t>16. Chi phí thuế TNDN hoãn lại</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr"/>
-      <c r="D23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="30" t="n">
+      <c r="C23" s="31" t="inlineStr"/>
+      <c r="D23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>17. LỢI NHUẬN SAU THUẾ TNDN (60 = 50 - 51 - 52)</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr"/>
-      <c r="D24" s="33" t="n">
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="36" t="n">
         <v>3099750122</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="E24" s="36" t="n">
         <v>4332093228</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="36" t="n">
         <v>7431843350</v>
       </c>
-      <c r="G24" s="33" t="n">
-        <v>1232343106</v>
-      </c>
-      <c r="H24" s="34" t="n">
+      <c r="G24" s="37" t="n">
         <v>0.3975620800056218</v>
       </c>
     </row>
@@ -2868,9 +2817,9 @@
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -2889,9 +2838,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>Cho các giai đoạn: Quý 1, Quý 2 và 6 tháng năm 2026 (Đơn vị tính: VNĐ)</t>
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Đơn vị tính: VNĐ - Dòng tiền qua 2 kỳ</t>
         </is>
       </c>
     </row>
@@ -2924,21 +2873,21 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Lũy kế 6T/2026</t>
+          <t>Tổng các kỳ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>I. LƯU CHUYỂN TIỀN TỪ HOẠT ĐỘNG KINH DOANH</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr"/>
-      <c r="C7" s="25" t="inlineStr"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
+      <c r="B7" s="28" t="inlineStr"/>
+      <c r="C7" s="28" t="inlineStr"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -2946,19 +2895,19 @@
           <t>1. Lợi nhuận trước thuế</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr"/>
-      <c r="D8" s="29" t="n">
+      <c r="C8" s="31" t="inlineStr"/>
+      <c r="D8" s="32" t="n">
         <v>3878437653</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="32" t="n">
         <v>5418866535</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="32" t="n">
         <v>9297304188</v>
       </c>
     </row>
@@ -2968,8 +2917,8 @@
           <t>2. Điều chỉnh cho các khoản:</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr"/>
-      <c r="C9" s="28" t="inlineStr"/>
+      <c r="B9" s="31" t="inlineStr"/>
+      <c r="C9" s="31" t="inlineStr"/>
       <c r="D9" s="14" t="n"/>
       <c r="E9" s="14" t="n"/>
       <c r="F9" s="14" t="n"/>
@@ -2980,41 +2929,41 @@
           <t xml:space="preserve">   - Khấu hao TSCĐ (TK 214)</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr"/>
-      <c r="D10" s="29" t="n">
+      <c r="C10" s="31" t="inlineStr"/>
+      <c r="D10" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="32" t="n">
         <v>11451510</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>3. Lợi nhuận từ HĐKD trước thay đổi vốn lưu động</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr"/>
-      <c r="D11" s="26" t="n">
+      <c r="C11" s="28" t="inlineStr"/>
+      <c r="D11" s="29" t="n">
         <v>3884163408</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="29" t="n">
         <v>5424592290</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <v>9308755698</v>
       </c>
     </row>
@@ -3024,19 +2973,19 @@
           <t xml:space="preserve">   - Tăng/giảm các khoản phải thu (TK 138, 141, 133)</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr"/>
-      <c r="D12" s="29" t="n">
+      <c r="C12" s="31" t="inlineStr"/>
+      <c r="D12" s="32" t="n">
         <v>9841744175</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="32" t="n">
         <v>-11571670238</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="32" t="n">
         <v>-1729926063</v>
       </c>
     </row>
@@ -3046,19 +2995,19 @@
           <t xml:space="preserve">   - Tăng/giảm chi phí trả trước (TK 242)</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr"/>
-      <c r="D13" s="29" t="n">
+      <c r="C13" s="31" t="inlineStr"/>
+      <c r="D13" s="32" t="n">
         <v>175932000</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="32" t="n">
         <v>58644000</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="32" t="n">
         <v>234576000</v>
       </c>
     </row>
@@ -3068,19 +3017,19 @@
           <t xml:space="preserve">   - Tăng/giảm các khoản phải trả (TK 333, 334, 335, 338, 353)</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr"/>
-      <c r="D14" s="29" t="n">
+      <c r="C14" s="31" t="inlineStr"/>
+      <c r="D14" s="32" t="n">
         <v>-223546738518</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="32" t="n">
         <v>79426597441</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="32" t="n">
         <v>-144120141077</v>
       </c>
     </row>
@@ -3090,55 +3039,55 @@
           <t xml:space="preserve">   - Tiền thuế TNDN đã nộp (TK 3334)</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr"/>
-      <c r="D15" s="29" t="n">
+      <c r="C15" s="31" t="inlineStr"/>
+      <c r="D15" s="32" t="n">
         <v>-1699375943</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="32" t="n">
         <v>-500000000</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="32" t="n">
         <v>-2199375943</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ HĐKD</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr"/>
-      <c r="D16" s="33" t="n">
+      <c r="C16" s="35" t="inlineStr"/>
+      <c r="D16" s="36" t="n">
         <v>-211344274878</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="36" t="n">
         <v>72838163493</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="36" t="n">
         <v>-138506111385</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>II. LƯU CHUYỂN TIỀN TỪ HOẠT ĐỘNG ĐẦU TƯ</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr"/>
-      <c r="C17" s="25" t="inlineStr"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
+      <c r="B17" s="28" t="inlineStr"/>
+      <c r="C17" s="28" t="inlineStr"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -3146,163 +3095,163 @@
           <t>1. Tiền chi gửi tiền có kỳ hạn / thu hồi tiền gửi (TK 1281-dài)</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr"/>
-      <c r="D18" s="29" t="n">
+      <c r="C18" s="31" t="inlineStr"/>
+      <c r="D18" s="32" t="n">
         <v>-16000000000</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="32" t="n">
         <v>-1000000000</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="32" t="n">
         <v>-17000000000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ HĐĐT</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr"/>
-      <c r="D19" s="33" t="n">
+      <c r="C19" s="35" t="inlineStr"/>
+      <c r="D19" s="36" t="n">
         <v>-16000000000</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="36" t="n">
         <v>-1000000000</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="36" t="n">
         <v>-17000000000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>III. LƯU CHUYỂN TIỀN TỪ HOẠT ĐỘNG TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr"/>
-      <c r="C20" s="25" t="inlineStr"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
+      <c r="B20" s="28" t="inlineStr"/>
+      <c r="C20" s="28" t="inlineStr"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ HĐTC</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr"/>
-      <c r="D21" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="33" t="n">
+      <c r="C21" s="35" t="inlineStr"/>
+      <c r="D21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>LƯU CHUYỂN TIỀN THUẦN TRONG KỲ (50 = 20 + 30 + 40)</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr"/>
-      <c r="D22" s="33" t="n">
+      <c r="C22" s="35" t="inlineStr"/>
+      <c r="D22" s="36" t="n">
         <v>-227344274878</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="36" t="n">
         <v>71838163493</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="36" t="n">
         <v>-155506111385</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền đầu kỳ</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr"/>
-      <c r="D23" s="26" t="n">
+      <c r="C23" s="28" t="inlineStr"/>
+      <c r="D23" s="29" t="n">
         <v>349015806508</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="29" t="n">
         <v>121671531630</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="29" t="n">
         <v>349015806508</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>TIỀN VÀ TƯƠNG ĐƯƠNG TIỀN CUỐI KỲ (70 = 50 + 60)</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr"/>
-      <c r="D24" s="33" t="n">
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="36" t="n">
         <v>121671531630</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="E24" s="36" t="n">
         <v>193509695123</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="36" t="n">
         <v>193509695123</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>Kiểm tra khớp số dư Tiền BCĐKT (Mã 110 - Mã 70)</t>
         </is>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>CHK</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr"/>
-      <c r="D25" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="37" t="n">
+      <c r="C25" s="39" t="inlineStr"/>
+      <c r="D25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3322,31 +3271,31 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>BẢNG ĐỐI CHIẾU SỐ DƯ &amp; PHÁT SINH CÁC TÀI KHOẢN (CẤP 1 &amp; CẤP 2)</t>
+          <t>BẢNG TỔNG HỢP SỐ DƯ &amp; PHÁT SINH CÁC TÀI KHOẢN (CẤP 1 &amp; CẤP 2)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết số liệu đối chiếu kiểm toán theo chuẩn kế toán Việt Nam</t>
+          <t>Đối chiếu kiểm toán đa kỳ - Năm 2026 (Đơn vị tính: VNĐ)</t>
         </is>
       </c>
     </row>
@@ -3364,107 +3313,107 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Dư Nợ ĐK (01/01)</t>
+          <t>Dư Nợ ĐK (01/01/2026)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Dư Có ĐK (01/01)</t>
+          <t>Dư Có ĐK (01/01/2026)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>PS Nợ Q1</t>
+          <t>PS Nợ Quý 1/2026</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>PS Có Q1</t>
+          <t>PS Có Quý 1/2026</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Dư Nợ Q1 (31/03)</t>
+          <t>Dư Nợ Cuối Quý 1/2026</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Dư Có Q1 (31/03)</t>
+          <t>Dư Có Cuối Quý 1/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>PS Nợ Q2</t>
+          <t>PS Nợ Quý 2/2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>PS Có Q2</t>
+          <t>PS Có Quý 2/2026</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Dư Nợ Q2 (30/06)</t>
+          <t>Dư Nợ Cuối Quý 2/2026</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Dư Có Q2 (30/06)</t>
+          <t>Dư Có Cuối Quý 2/2026</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Biến động Dư ròng Q2/Q1</t>
+          <t>Biến động Dư ròng</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Tiền mặt</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="29" t="n">
         <v>310486901</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="26" t="n">
+      <c r="D6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="29" t="n">
         <v>382976974</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="29" t="n">
         <v>331744738</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="29" t="n">
         <v>361719137</v>
       </c>
-      <c r="H6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="26" t="n">
+      <c r="H6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29" t="n">
         <v>3748413</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="29" t="n">
         <v>84560073</v>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="29" t="n">
         <v>280907477</v>
       </c>
-      <c r="L6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="26" t="n">
-        <v>-80811660</v>
+      <c r="L6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="29" t="n">
+        <v>-29579424</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>1111</t>
         </is>
@@ -3474,87 +3423,87 @@
           <t>Tiền Việt Nam</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="32" t="n">
         <v>310486901</v>
       </c>
-      <c r="D7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="29" t="n">
+      <c r="D7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="32" t="n">
         <v>382976974</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="32" t="n">
         <v>331744738</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="32" t="n">
         <v>361719137</v>
       </c>
-      <c r="H7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="H7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="32" t="n">
         <v>3748413</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="32" t="n">
         <v>84560073</v>
       </c>
-      <c r="K7" s="29" t="n">
+      <c r="K7" s="32" t="n">
         <v>280907477</v>
       </c>
-      <c r="L7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="29" t="n">
-        <v>-80811660</v>
+      <c r="L7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="32" t="n">
+        <v>-29579424</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Tiền gửi không kỳ hạn</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="29" t="n">
         <v>339705319607</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="26" t="n">
+      <c r="D8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29" t="n">
         <v>18560663533790</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="29" t="n">
         <v>18779059040904</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="29" t="n">
         <v>121309812493</v>
       </c>
-      <c r="H8" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="26" t="n">
+      <c r="H8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29" t="n">
         <v>25332481951634</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="29" t="n">
         <v>25260562976481</v>
       </c>
-      <c r="K8" s="26" t="n">
+      <c r="K8" s="29" t="n">
         <v>193228787646</v>
       </c>
-      <c r="L8" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="26" t="n">
-        <v>71918975153</v>
+      <c r="L8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="29" t="n">
+        <v>-146476531961</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>1121</t>
         </is>
@@ -3564,42 +3513,42 @@
           <t>Tiền Việt Nam</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="32" t="n">
         <v>299738414128</v>
       </c>
-      <c r="D9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29" t="n">
+      <c r="D9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="32" t="n">
         <v>10364202871348</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="32" t="n">
         <v>10589466947147</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="32" t="n">
         <v>74474338329</v>
       </c>
-      <c r="H9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="29" t="n">
+      <c r="H9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="32" t="n">
         <v>13520720040074</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="32" t="n">
         <v>13514931934911</v>
       </c>
-      <c r="K9" s="29" t="n">
+      <c r="K9" s="32" t="n">
         <v>80262443492</v>
       </c>
-      <c r="L9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="29" t="n">
-        <v>5788105163</v>
+      <c r="L9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="32" t="n">
+        <v>-219475970636</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
@@ -3609,87 +3558,87 @@
           <t>Ngoại tệ</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="32" t="n">
         <v>39966905479</v>
       </c>
-      <c r="D10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="29" t="n">
+      <c r="D10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32" t="n">
         <v>8196460662442</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="32" t="n">
         <v>8189592093757</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="32" t="n">
         <v>46835474164</v>
       </c>
-      <c r="H10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="29" t="n">
+      <c r="H10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="32" t="n">
         <v>11811761911560</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="32" t="n">
         <v>11745631041570</v>
       </c>
-      <c r="K10" s="29" t="n">
+      <c r="K10" s="32" t="n">
         <v>112966344154</v>
       </c>
-      <c r="L10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="29" t="n">
-        <v>66130869990</v>
+      <c r="L10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="32" t="n">
+        <v>72999438675</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="29" t="n">
         <v>58000000000</v>
       </c>
-      <c r="D11" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="26" t="n">
+      <c r="D11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <v>57000000000</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <v>50000000000</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="29" t="n">
         <v>65000000000</v>
       </c>
-      <c r="H11" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="26" t="n">
+      <c r="H11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="29" t="n">
         <v>31000000000</v>
       </c>
-      <c r="J11" s="26" t="n">
+      <c r="J11" s="29" t="n">
         <v>30000000000</v>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="K11" s="29" t="n">
         <v>66000000000</v>
       </c>
-      <c r="L11" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="26" t="n">
-        <v>1000000000</v>
+      <c r="L11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>8000000000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>1281</t>
         </is>
@@ -3699,87 +3648,87 @@
           <t>Tiền gửi có kỳ hạn</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="32" t="n">
         <v>58000000000</v>
       </c>
-      <c r="D12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29" t="n">
+      <c r="D12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="32" t="n">
         <v>57000000000</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="32" t="n">
         <v>65000000000</v>
       </c>
-      <c r="H12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="29" t="n">
+      <c r="H12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="32" t="n">
         <v>31000000000</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="32" t="n">
         <v>30000000000</v>
       </c>
-      <c r="K12" s="29" t="n">
+      <c r="K12" s="32" t="n">
         <v>66000000000</v>
       </c>
-      <c r="L12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="29" t="n">
-        <v>1000000000</v>
+      <c r="L12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="32" t="n">
+        <v>8000000000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Thuế GTGT được khấu trừ</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="26" t="n">
+      <c r="C13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <v>286565983</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="29" t="n">
         <v>286565983</v>
       </c>
-      <c r="G13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="26" t="n">
+      <c r="G13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="29" t="n">
         <v>333363382</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="29" t="n">
         <v>333363382</v>
       </c>
-      <c r="K13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="26" t="n">
+      <c r="K13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
@@ -3789,87 +3738,87 @@
           <t>Thuế GTGT được khấu trừ của hàng hóa, dịch vụ</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
+      <c r="C14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="32" t="n">
         <v>286565983</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="32" t="n">
         <v>286565983</v>
       </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
+      <c r="G14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="32" t="n">
         <v>333363382</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="32" t="n">
         <v>333363382</v>
       </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
+      <c r="K14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Phải thu khác</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="29" t="n">
         <v>42046942920</v>
       </c>
-      <c r="D15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="26" t="n">
+      <c r="D15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29" t="n">
         <v>1561166305841</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="29" t="n">
         <v>1571008050016</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="29" t="n">
         <v>32205198745</v>
       </c>
-      <c r="H15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="26" t="n">
+      <c r="H15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="29" t="n">
         <v>1514291765558</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="29" t="n">
         <v>1502720095320</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="29" t="n">
         <v>43776868983</v>
       </c>
-      <c r="L15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="26" t="n">
-        <v>11571670238</v>
+      <c r="L15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="29" t="n">
+        <v>1729926063</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
@@ -3879,87 +3828,87 @@
           <t>Phải thu khác</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="32" t="n">
         <v>42046942920</v>
       </c>
-      <c r="D16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="29" t="n">
+      <c r="D16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="32" t="n">
         <v>1561166305841</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="32" t="n">
         <v>1571008050016</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="32" t="n">
         <v>32205198745</v>
       </c>
-      <c r="H16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="29" t="n">
+      <c r="H16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="32" t="n">
         <v>1514291765558</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="32" t="n">
         <v>1502720095320</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K16" s="32" t="n">
         <v>43776868983</v>
       </c>
-      <c r="L16" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="29" t="n">
-        <v>11571670238</v>
+      <c r="L16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="32" t="n">
+        <v>1729926063</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Tạm ứng</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="26" t="n">
+      <c r="C17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29" t="n">
         <v>27000000</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="29" t="n">
         <v>27000000</v>
       </c>
-      <c r="G17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="26" t="n">
+      <c r="G17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="29" t="n">
         <v>27000000</v>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="29" t="n">
         <v>27000000</v>
       </c>
-      <c r="K17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="26" t="n">
+      <c r="K17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>1411</t>
         </is>
@@ -3969,87 +3918,87 @@
           <t>Tạm ứng để hoạt động nghiệp vụ</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
+      <c r="C18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="32" t="n">
         <v>27000000</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="32" t="n">
         <v>27000000</v>
       </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
+      <c r="G18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="32" t="n">
         <v>27000000</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="32" t="n">
         <v>27000000</v>
       </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
+      <c r="K18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Tài sản cố định hữu hình</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="29" t="n">
         <v>2778069546</v>
       </c>
-      <c r="D19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="26" t="n">
+      <c r="D19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="29" t="n">
         <v>102838182</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="29" t="n">
         <v>2675231364</v>
       </c>
-      <c r="H19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="26" t="n">
+      <c r="H19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="29" t="n">
         <v>2675231364</v>
       </c>
-      <c r="L19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="26" t="n">
-        <v>0</v>
+      <c r="L19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="29" t="n">
+        <v>-102838182</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>2112</t>
         </is>
@@ -4059,42 +4008,42 @@
           <t>Máy móc, thiết bị</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="32" t="n">
         <v>118875001</v>
       </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
+      <c r="D20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="32" t="n">
         <v>118875001</v>
       </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
+      <c r="H20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="32" t="n">
         <v>118875001</v>
       </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
+      <c r="L20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
@@ -4104,42 +4053,42 @@
           <t>Phương tiện vận tải, truyền dẫn</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="32" t="n">
         <v>2356156363</v>
       </c>
-      <c r="D21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="29" t="n">
+      <c r="D21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="32" t="n">
         <v>2356156363</v>
       </c>
-      <c r="H21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="29" t="n">
+      <c r="H21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="32" t="n">
         <v>2356156363</v>
       </c>
-      <c r="L21" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="29" t="n">
+      <c r="L21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>2114</t>
         </is>
@@ -4149,42 +4098,42 @@
           <t>Thiết bị, dụng cụ quản lý</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="32" t="n">
         <v>232918182</v>
       </c>
-      <c r="D22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="29" t="n">
+      <c r="D22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="32" t="n">
         <v>32718182</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="32" t="n">
         <v>200200000</v>
       </c>
-      <c r="H22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="29" t="n">
+      <c r="H22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="32" t="n">
         <v>200200000</v>
       </c>
-      <c r="L22" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="29" t="n">
-        <v>0</v>
+      <c r="L22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="32" t="n">
+        <v>-32718182</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>2118</t>
         </is>
@@ -4194,87 +4143,87 @@
           <t>TSCĐ khác</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="32" t="n">
         <v>70120000</v>
       </c>
-      <c r="D23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="29" t="n">
+      <c r="D23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="32" t="n">
         <v>70120000</v>
       </c>
-      <c r="G23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="29" t="n">
-        <v>0</v>
+      <c r="G23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="32" t="n">
+        <v>-70120000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Hao mòn tài sản cố định</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="26" t="n">
+      <c r="C24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="29" t="n">
         <v>2737373558</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="29" t="n">
         <v>102838182</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="29" t="n">
         <v>5725755</v>
       </c>
-      <c r="G24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="26" t="n">
+      <c r="G24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="29" t="n">
         <v>2640261131</v>
       </c>
-      <c r="I24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="26" t="n">
+      <c r="I24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="29" t="n">
         <v>5725755</v>
       </c>
-      <c r="K24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="26" t="n">
+      <c r="K24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="29" t="n">
         <v>2645986886</v>
       </c>
-      <c r="M24" s="26" t="n">
-        <v>-5725755</v>
+      <c r="M24" s="29" t="n">
+        <v>91386672</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>2141</t>
         </is>
@@ -4284,87 +4233,87 @@
           <t>Hao mòn TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="29" t="n">
+      <c r="C25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="32" t="n">
         <v>2737373558</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="32" t="n">
         <v>102838182</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="G25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="29" t="n">
+      <c r="G25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="32" t="n">
         <v>2640261131</v>
       </c>
-      <c r="I25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="29" t="n">
+      <c r="I25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="K25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="29" t="n">
+      <c r="K25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="32" t="n">
         <v>2645986886</v>
       </c>
-      <c r="M25" s="29" t="n">
-        <v>-5725755</v>
+      <c r="M25" s="32" t="n">
+        <v>91386672</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>Chi phí chờ phân bổ</t>
         </is>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="29" t="n">
         <v>234576000</v>
       </c>
-      <c r="D26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="26" t="n">
+      <c r="D26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="29" t="n">
         <v>175932000</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="29" t="n">
         <v>58644000</v>
       </c>
-      <c r="H26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="26" t="n">
+      <c r="H26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="29" t="n">
         <v>58644000</v>
       </c>
-      <c r="K26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="26" t="n">
-        <v>-58644000</v>
+      <c r="K26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="29" t="n">
+        <v>-234576000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>2421</t>
         </is>
@@ -4374,87 +4323,87 @@
           <t>Chi phí trả trước ngắn hạn</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="32" t="n">
         <v>234576000</v>
       </c>
-      <c r="D27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="29" t="n">
+      <c r="D27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="32" t="n">
         <v>175932000</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="32" t="n">
         <v>58644000</v>
       </c>
-      <c r="H27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="29" t="n">
+      <c r="H27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="32" t="n">
         <v>58644000</v>
       </c>
-      <c r="K27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="29" t="n">
-        <v>-58644000</v>
+      <c r="K27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="32" t="n">
+        <v>-234576000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Ký quỹ, ký cược</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="D28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="26" t="n">
+      <c r="D28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="H28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="26" t="n">
+      <c r="H28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="29" t="n">
         <v>15000000</v>
       </c>
-      <c r="L28" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="26" t="n">
+      <c r="L28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>2441</t>
         </is>
@@ -4464,87 +4413,87 @@
           <t>Ký quỹ, ký cược dài hạn</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="D29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="29" t="n">
+      <c r="D29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="H29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="29" t="n">
+      <c r="H29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="32" t="n">
         <v>15000000</v>
       </c>
-      <c r="L29" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="29" t="n">
+      <c r="L29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Thuế và các khoản phải nộp Nhà nước</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="26" t="n">
+      <c r="C30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="29" t="n">
         <v>2104207557</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="29" t="n">
         <v>3515890761</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="29" t="n">
         <v>2533921770</v>
       </c>
-      <c r="G30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="26" t="n">
+      <c r="G30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="29" t="n">
         <v>1122238566</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="29" t="n">
         <v>1894092838</v>
       </c>
-      <c r="J30" s="26" t="n">
+      <c r="J30" s="29" t="n">
         <v>2575387900</v>
       </c>
-      <c r="K30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="26" t="n">
+      <c r="K30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="29" t="n">
         <v>1803533628</v>
       </c>
-      <c r="M30" s="26" t="n">
-        <v>-681295062</v>
+      <c r="M30" s="29" t="n">
+        <v>300673929</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>3331</t>
         </is>
@@ -4554,42 +4503,42 @@
           <t>Thuế giá trị gia tăng phải nộp</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="29" t="n">
+      <c r="C31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="32" t="n">
         <v>327740170</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="32" t="n">
         <v>1211085768</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="32" t="n">
         <v>1216547100</v>
       </c>
-      <c r="G31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="29" t="n">
+      <c r="G31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="32" t="n">
         <v>333201502</v>
       </c>
-      <c r="I31" s="29" t="n">
+      <c r="I31" s="32" t="n">
         <v>1311751576</v>
       </c>
-      <c r="J31" s="29" t="n">
+      <c r="J31" s="32" t="n">
         <v>1335096028</v>
       </c>
-      <c r="K31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="29" t="n">
+      <c r="K31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="32" t="n">
         <v>356545954</v>
       </c>
-      <c r="M31" s="29" t="n">
-        <v>-23344452</v>
+      <c r="M31" s="32" t="n">
+        <v>-28805784</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>3334</t>
         </is>
@@ -4599,42 +4548,42 @@
           <t>Thuế thu nhập doanh nghiệp</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="29" t="n">
+      <c r="C32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="32" t="n">
         <v>1699375943</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="32" t="n">
         <v>1699375943</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="32" t="n">
         <v>778687531</v>
       </c>
-      <c r="G32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="29" t="n">
+      <c r="G32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="32" t="n">
         <v>778687531</v>
       </c>
-      <c r="I32" s="29" t="n">
+      <c r="I32" s="32" t="n">
         <v>500000000</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="32" t="n">
         <v>1086773307</v>
       </c>
-      <c r="K32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="29" t="n">
+      <c r="K32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="32" t="n">
         <v>1365460838</v>
       </c>
-      <c r="M32" s="29" t="n">
-        <v>-586773307</v>
+      <c r="M32" s="32" t="n">
+        <v>333915105</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>3335</t>
         </is>
@@ -4644,42 +4593,42 @@
           <t>Thuế thu nhập cá nhân</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="29" t="n">
+      <c r="C33" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="32" t="n">
         <v>77091444</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="32" t="n">
         <v>603227946</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="32" t="n">
         <v>536486035</v>
       </c>
-      <c r="G33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="29" t="n">
+      <c r="G33" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="32" t="n">
         <v>10349533</v>
       </c>
-      <c r="I33" s="29" t="n">
+      <c r="I33" s="32" t="n">
         <v>80350426</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="32" t="n">
         <v>151527729</v>
       </c>
-      <c r="K33" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="29" t="n">
+      <c r="K33" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="32" t="n">
         <v>81526836</v>
       </c>
-      <c r="M33" s="29" t="n">
-        <v>-71177303</v>
+      <c r="M33" s="32" t="n">
+        <v>-4435392</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>3338</t>
         </is>
@@ -4689,87 +4638,87 @@
           <t>Thuế bảo vệ môi trường và các loại thuế khác</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="29" t="n">
+      <c r="C34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="32" t="n">
         <v>2201104</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="32" t="n">
         <v>2201104</v>
       </c>
-      <c r="G34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="29" t="n">
+      <c r="G34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="32" t="n">
         <v>1990836</v>
       </c>
-      <c r="J34" s="29" t="n">
+      <c r="J34" s="32" t="n">
         <v>1990836</v>
       </c>
-      <c r="K34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="29" t="n">
+      <c r="K34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>334</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>Phải trả người lao động</t>
         </is>
       </c>
-      <c r="C35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="26" t="n">
+      <c r="C35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="29" t="n">
         <v>5432454882</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="29" t="n">
         <v>7111945353</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="29" t="n">
         <v>3897402000</v>
       </c>
-      <c r="G35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="26" t="n">
+      <c r="G35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="29" t="n">
         <v>2217911529</v>
       </c>
-      <c r="I35" s="26" t="n">
+      <c r="I35" s="29" t="n">
         <v>3454428095</v>
       </c>
-      <c r="J35" s="26" t="n">
+      <c r="J35" s="29" t="n">
         <v>3916542218</v>
       </c>
-      <c r="K35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="26" t="n">
+      <c r="K35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="29" t="n">
         <v>2680025652</v>
       </c>
-      <c r="M35" s="26" t="n">
-        <v>-462114123</v>
+      <c r="M35" s="29" t="n">
+        <v>2752429230</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>3341</t>
         </is>
@@ -4779,87 +4728,87 @@
           <t>Phải trả công nhân viên</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="29" t="n">
+      <c r="C36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="32" t="n">
         <v>5432454882</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="32" t="n">
         <v>7111945353</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="32" t="n">
         <v>3897402000</v>
       </c>
-      <c r="G36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="29" t="n">
+      <c r="G36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="32" t="n">
         <v>2217911529</v>
       </c>
-      <c r="I36" s="29" t="n">
+      <c r="I36" s="32" t="n">
         <v>3454428095</v>
       </c>
-      <c r="J36" s="29" t="n">
+      <c r="J36" s="32" t="n">
         <v>3916542218</v>
       </c>
-      <c r="K36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="29" t="n">
+      <c r="K36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="32" t="n">
         <v>2680025652</v>
       </c>
-      <c r="M36" s="29" t="n">
-        <v>-462114123</v>
+      <c r="M36" s="32" t="n">
+        <v>2752429230</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>Chi phí phải trả</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="26" t="n">
+      <c r="C37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="29" t="n">
         <v>1552685577</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="29" t="n">
         <v>163640000</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="29" t="n">
         <v>721837270</v>
       </c>
-      <c r="G37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="26" t="n">
+      <c r="G37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="29" t="n">
         <v>2110882847</v>
       </c>
-      <c r="I37" s="26" t="n">
+      <c r="I37" s="29" t="n">
         <v>88000000</v>
       </c>
-      <c r="J37" s="26" t="n">
+      <c r="J37" s="29" t="n">
         <v>1151136793</v>
       </c>
-      <c r="K37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="26" t="n">
+      <c r="K37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="29" t="n">
         <v>3174019640</v>
       </c>
-      <c r="M37" s="26" t="n">
-        <v>-1063136793</v>
+      <c r="M37" s="29" t="n">
+        <v>-1621334063</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>3351</t>
         </is>
@@ -4869,87 +4818,87 @@
           <t>Chi phí phải trả</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="29" t="n">
+      <c r="C38" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="32" t="n">
         <v>1552685577</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="32" t="n">
         <v>163640000</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="32" t="n">
         <v>721837270</v>
       </c>
-      <c r="G38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="29" t="n">
+      <c r="G38" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="32" t="n">
         <v>2110882847</v>
       </c>
-      <c r="I38" s="29" t="n">
+      <c r="I38" s="32" t="n">
         <v>88000000</v>
       </c>
-      <c r="J38" s="29" t="n">
+      <c r="J38" s="32" t="n">
         <v>1151136793</v>
       </c>
-      <c r="K38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="29" t="n">
+      <c r="K38" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="32" t="n">
         <v>3174019640</v>
       </c>
-      <c r="M38" s="29" t="n">
-        <v>-1063136793</v>
+      <c r="M38" s="32" t="n">
+        <v>-1621334063</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>338</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Phải trả, phải nộp khác</t>
         </is>
       </c>
-      <c r="C39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="26" t="n">
+      <c r="C39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="29" t="n">
         <v>353628589247</v>
       </c>
-      <c r="E39" s="26" t="n">
+      <c r="E39" s="29" t="n">
         <v>18723247983105</v>
       </c>
-      <c r="F39" s="26" t="n">
+      <c r="F39" s="29" t="n">
         <v>18502838871249</v>
       </c>
-      <c r="G39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="26" t="n">
+      <c r="G39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="29" t="n">
         <v>133219477391</v>
       </c>
-      <c r="I39" s="26" t="n">
+      <c r="I39" s="29" t="n">
         <v>25228928210356</v>
       </c>
-      <c r="J39" s="26" t="n">
+      <c r="J39" s="29" t="n">
         <v>25306736535126</v>
       </c>
-      <c r="K39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="26" t="n">
+      <c r="K39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="29" t="n">
         <v>211027802161</v>
       </c>
-      <c r="M39" s="26" t="n">
-        <v>-77808324770</v>
+      <c r="M39" s="29" t="n">
+        <v>142600787086</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>3382</t>
         </is>
@@ -4959,42 +4908,42 @@
           <t>Kinh phí công đoàn</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="29" t="n">
+      <c r="C40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="32" t="n">
         <v>9470328</v>
       </c>
-      <c r="G40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="29" t="n">
+      <c r="G40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="32" t="n">
         <v>9470328</v>
       </c>
-      <c r="I40" s="29" t="n">
+      <c r="I40" s="32" t="n">
         <v>9470328</v>
       </c>
-      <c r="J40" s="29" t="n">
+      <c r="J40" s="32" t="n">
         <v>9417445</v>
       </c>
-      <c r="K40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="29" t="n">
+      <c r="K40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="32" t="n">
         <v>9417445</v>
       </c>
-      <c r="M40" s="29" t="n">
-        <v>52883</v>
+      <c r="M40" s="32" t="n">
+        <v>-9417445</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>3383</t>
         </is>
@@ -5004,42 +4953,42 @@
           <t>Bảo hiểm xã hội</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="29" t="n">
+      <c r="C41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="32" t="n">
         <v>1251923</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="32" t="n">
         <v>276971310</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="32" t="n">
         <v>276971310</v>
       </c>
-      <c r="G41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="29" t="n">
+      <c r="G41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="32" t="n">
         <v>1251923</v>
       </c>
-      <c r="I41" s="29" t="n">
+      <c r="I41" s="32" t="n">
         <v>274568700</v>
       </c>
-      <c r="J41" s="29" t="n">
+      <c r="J41" s="32" t="n">
         <v>274568700</v>
       </c>
-      <c r="K41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="29" t="n">
+      <c r="K41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="32" t="n">
         <v>1251923</v>
       </c>
-      <c r="M41" s="29" t="n">
+      <c r="M41" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>3384</t>
         </is>
@@ -5049,42 +4998,42 @@
           <t>Bảo hiểm y tế</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="29" t="n">
+      <c r="C42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="32" t="n">
         <v>48877290</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="32" t="n">
         <v>48877290</v>
       </c>
-      <c r="G42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="29" t="n">
+      <c r="G42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="32" t="n">
         <v>48877290</v>
       </c>
-      <c r="J42" s="29" t="n">
+      <c r="J42" s="32" t="n">
         <v>48877290</v>
       </c>
-      <c r="K42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="29" t="n">
+      <c r="K42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>3386</t>
         </is>
@@ -5094,42 +5043,42 @@
           <t>Bảo hiểm thất nghiệp</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="29" t="n">
+      <c r="C43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="32" t="n">
         <v>21723240</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="32" t="n">
         <v>21723240</v>
       </c>
-      <c r="G43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="29" t="n">
+      <c r="G43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="32" t="n">
         <v>21534800</v>
       </c>
-      <c r="J43" s="29" t="n">
+      <c r="J43" s="32" t="n">
         <v>21534800</v>
       </c>
-      <c r="K43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="29" t="n">
+      <c r="K43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>3388</t>
         </is>
@@ -5139,222 +5088,222 @@
           <t>Phải trả, phải nộp khác</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="29" t="n">
+      <c r="C44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="32" t="n">
         <v>353627337324</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="32" t="n">
         <v>18722900411265</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="32" t="n">
         <v>18502481829081</v>
       </c>
-      <c r="G44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="29" t="n">
+      <c r="G44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="32" t="n">
         <v>133208755140</v>
       </c>
-      <c r="I44" s="29" t="n">
+      <c r="I44" s="32" t="n">
         <v>25228573759238</v>
       </c>
-      <c r="J44" s="29" t="n">
+      <c r="J44" s="32" t="n">
         <v>25306382136891</v>
       </c>
-      <c r="K44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="29" t="n">
+      <c r="K44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="32" t="n">
         <v>211017132793</v>
       </c>
-      <c r="M44" s="29" t="n">
-        <v>-77808377653</v>
+      <c r="M44" s="32" t="n">
+        <v>142610204531</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>Quỹ khen thưởng, phúc lợi</t>
         </is>
       </c>
-      <c r="C45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="26" t="n">
+      <c r="C45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="29" t="n">
         <v>538136029</v>
       </c>
-      <c r="E45" s="26" t="n">
+      <c r="E45" s="29" t="n">
         <v>420000000</v>
       </c>
-      <c r="F45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="26" t="n">
+      <c r="F45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="29" t="n">
         <v>118136029</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I45" s="29" t="n">
         <v>4500000</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J45" s="29" t="n">
         <v>3000000</v>
       </c>
-      <c r="K45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="26" t="n">
+      <c r="K45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="29" t="n">
         <v>116636029</v>
       </c>
-      <c r="M45" s="26" t="n">
+      <c r="M45" s="29" t="n">
+        <v>421500000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Quỹ khen thưởng</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>448921461</v>
+      </c>
+      <c r="E46" s="32" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="F46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="32" t="n">
+        <v>28921461</v>
+      </c>
+      <c r="I46" s="32" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J46" s="32" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="32" t="n">
+        <v>28921461</v>
+      </c>
+      <c r="M46" s="32" t="n">
+        <v>420000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Quỹ phúc lợi</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>89214568</v>
+      </c>
+      <c r="E47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="32" t="n">
+        <v>89214568</v>
+      </c>
+      <c r="I47" s="32" t="n">
         <v>1500000</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>3531</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Quỹ khen thưởng</t>
-        </is>
-      </c>
-      <c r="C46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="29" t="n">
-        <v>448921461</v>
-      </c>
-      <c r="E46" s="29" t="n">
-        <v>420000000</v>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="29" t="n">
-        <v>28921461</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J46" s="29" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="29" t="n">
-        <v>28921461</v>
-      </c>
-      <c r="M46" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="28" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Quỹ phúc lợi</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="29" t="n">
-        <v>89214568</v>
-      </c>
-      <c r="E47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>89214568</v>
-      </c>
-      <c r="I47" s="29" t="n">
+      <c r="J47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="32" t="n">
+        <v>87714568</v>
+      </c>
+      <c r="M47" s="32" t="n">
         <v>1500000</v>
       </c>
-      <c r="J47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="29" t="n">
-        <v>87714568</v>
-      </c>
-      <c r="M47" s="29" t="n">
-        <v>1500000</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Vốn đầu tư của chủ sở hữu</t>
         </is>
       </c>
-      <c r="C48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="26" t="n">
+      <c r="C48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="29" t="n">
         <v>50000000000</v>
       </c>
-      <c r="E48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="26" t="n">
+      <c r="E48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="29" t="n">
         <v>50000000000</v>
       </c>
-      <c r="I48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="26" t="n">
+      <c r="I48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="29" t="n">
         <v>50000000000</v>
       </c>
-      <c r="M48" s="26" t="n">
+      <c r="M48" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>4111</t>
         </is>
@@ -5364,87 +5313,87 @@
           <t>Vốn góp của chủ sở hữu</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="29" t="n">
+      <c r="C49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="E49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="29" t="n">
+      <c r="E49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="I49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="29" t="n">
+      <c r="I49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="32" t="n">
         <v>50000000000</v>
       </c>
-      <c r="M49" s="29" t="n">
+      <c r="M49" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>413</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>Chênh lệch tỷ giá hối đoái</t>
         </is>
       </c>
-      <c r="C50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="26" t="n">
+      <c r="C50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="29" t="n">
         <v>181114870</v>
       </c>
-      <c r="F50" s="26" t="n">
+      <c r="F50" s="29" t="n">
         <v>181114870</v>
       </c>
-      <c r="G50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="26" t="n">
+      <c r="G50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="29" t="n">
         <v>974090373</v>
       </c>
-      <c r="J50" s="26" t="n">
+      <c r="J50" s="29" t="n">
         <v>974090373</v>
       </c>
-      <c r="K50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="26" t="n">
+      <c r="K50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="28" t="inlineStr">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>4131</t>
         </is>
@@ -5454,87 +5403,87 @@
           <t>Chênh lệch tỷ giá do đánh giá lại các khoản mục tiền tệ có gốc ngoại tệ</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="29" t="n">
+      <c r="C51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="32" t="n">
         <v>181114870</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="32" t="n">
         <v>181114870</v>
       </c>
-      <c r="G51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="29" t="n">
+      <c r="G51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="32" t="n">
         <v>974090373</v>
       </c>
-      <c r="J51" s="29" t="n">
+      <c r="J51" s="32" t="n">
         <v>974090373</v>
       </c>
-      <c r="K51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="29" t="n">
+      <c r="K51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>Quỹ đầu tư phát triển</t>
         </is>
       </c>
-      <c r="C52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="26" t="n">
+      <c r="C52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="29" t="n">
         <v>5336258205</v>
       </c>
-      <c r="E52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="26" t="n">
+      <c r="E52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="29" t="n">
         <v>5336258205</v>
       </c>
-      <c r="I52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="26" t="n">
+      <c r="I52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="29" t="n">
         <v>5336258205</v>
       </c>
-      <c r="M52" s="26" t="n">
+      <c r="M52" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="inlineStr">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>4141</t>
         </is>
@@ -5544,87 +5493,87 @@
           <t>Quỹ đầu tư phát triển</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="29" t="n">
+      <c r="C53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="E53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="29" t="n">
+      <c r="E53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="I53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="29" t="n">
+      <c r="I53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="32" t="n">
         <v>5336258205</v>
       </c>
-      <c r="M53" s="29" t="n">
+      <c r="M53" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>418</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>Các quỹ khác thuộc vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="C54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="26" t="n">
+      <c r="C54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="29" t="n">
         <v>3793255874</v>
       </c>
-      <c r="E54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="26" t="n">
+      <c r="E54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="29" t="n">
         <v>3793255874</v>
       </c>
-      <c r="I54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="26" t="n">
+      <c r="I54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="29" t="n">
         <v>3793255874</v>
       </c>
-      <c r="M54" s="26" t="n">
+      <c r="M54" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>4181</t>
         </is>
@@ -5634,87 +5583,87 @@
           <t>Các quỹ thuộc vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="29" t="n">
+      <c r="C55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="E55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="29" t="n">
+      <c r="E55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="I55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="29" t="n">
+      <c r="I55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="32" t="n">
         <v>3793255874</v>
       </c>
-      <c r="M55" s="29" t="n">
+      <c r="M55" s="32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25" t="inlineStr">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>421</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>Lợi nhuận sau thuế chưa phân phối</t>
         </is>
       </c>
-      <c r="C56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="26" t="n">
+      <c r="C56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="E56" s="26" t="n">
+      <c r="E56" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="F56" s="26" t="n">
+      <c r="F56" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="G56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="26" t="n">
+      <c r="G56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="I56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="26" t="n">
+      <c r="I56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="29" t="n">
         <v>17967434045</v>
       </c>
-      <c r="M56" s="26" t="n">
+      <c r="M56" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28" t="inlineStr">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>4211</t>
         </is>
@@ -5724,42 +5673,42 @@
           <t>Lợi nhuận sau thuế chưa phân phối lũy kế đến cuối năm trước</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="29" t="n">
+      <c r="C57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="G57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="29" t="n">
+      <c r="G57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="I57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="29" t="n">
+      <c r="I57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="M57" s="29" t="n">
-        <v>0</v>
+      <c r="M57" s="32" t="n">
+        <v>-17967434045</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="inlineStr">
+      <c r="A58" s="31" t="inlineStr">
         <is>
           <t>4212</t>
         </is>
@@ -5769,87 +5718,87 @@
           <t>Lợi nhuận sau thuế chưa phân phối năm nay</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="29" t="n">
+      <c r="C58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="32" t="n">
         <v>17967434045</v>
       </c>
-      <c r="F58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="29" t="n">
-        <v>0</v>
+      <c r="F58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="32" t="n">
+        <v>17967434045</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="25" t="inlineStr">
+      <c r="A59" s="28" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ</t>
         </is>
       </c>
-      <c r="C59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="26" t="n">
+      <c r="C59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="29" t="n">
         <v>11955764348</v>
       </c>
-      <c r="G59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="26" t="n">
+      <c r="G59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="29" t="n">
         <v>11955764348</v>
       </c>
-      <c r="I59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="26" t="n">
+      <c r="I59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="29" t="n">
         <v>13273671288</v>
       </c>
-      <c r="K59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="26" t="n">
+      <c r="K59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="29" t="n">
         <v>25229435636</v>
       </c>
-      <c r="M59" s="26" t="n">
-        <v>-13273671288</v>
+      <c r="M59" s="29" t="n">
+        <v>-25229435636</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="inlineStr">
+      <c r="A60" s="31" t="inlineStr">
         <is>
           <t>5113</t>
         </is>
@@ -5859,87 +5808,87 @@
           <t>Doanh thu cung cấp dịch vụ</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="29" t="n">
+      <c r="C60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="32" t="n">
         <v>11955764348</v>
       </c>
-      <c r="G60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="29" t="n">
+      <c r="G60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="32" t="n">
         <v>11955764348</v>
       </c>
-      <c r="I60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="29" t="n">
+      <c r="I60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="32" t="n">
         <v>13273671288</v>
       </c>
-      <c r="K60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="29" t="n">
+      <c r="K60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="32" t="n">
         <v>25229435636</v>
       </c>
-      <c r="M60" s="29" t="n">
-        <v>-13273671288</v>
+      <c r="M60" s="32" t="n">
+        <v>-25229435636</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="25" t="inlineStr">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>515</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>Doanh thu hoạt động tài chính</t>
         </is>
       </c>
-      <c r="C61" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="26" t="n">
+      <c r="C61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="29" t="n">
         <v>52120548</v>
       </c>
-      <c r="F61" s="26" t="n">
+      <c r="F61" s="29" t="n">
         <v>1035187374</v>
       </c>
-      <c r="G61" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="26" t="n">
+      <c r="G61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="29" t="n">
         <v>983066826</v>
       </c>
-      <c r="I61" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="26" t="n">
+      <c r="I61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="29" t="n">
         <v>1428466738</v>
       </c>
-      <c r="K61" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="26" t="n">
+      <c r="K61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="29" t="n">
         <v>2411533564</v>
       </c>
-      <c r="M61" s="26" t="n">
-        <v>-1428466738</v>
+      <c r="M61" s="29" t="n">
+        <v>-2411533564</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="inlineStr">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>5151</t>
         </is>
@@ -5949,267 +5898,267 @@
           <t>Doanh thu hoạt động tài chính</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="29" t="n">
+      <c r="C62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="32" t="n">
         <v>52120548</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="32" t="n">
         <v>1035187374</v>
       </c>
-      <c r="G62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="29" t="n">
+      <c r="G62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="32" t="n">
         <v>983066826</v>
       </c>
-      <c r="I62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="29" t="n">
+      <c r="I62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="32" t="n">
         <v>1428466738</v>
       </c>
-      <c r="K62" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="29" t="n">
+      <c r="K62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="32" t="n">
         <v>2411533564</v>
       </c>
-      <c r="M62" s="29" t="n">
-        <v>-1428466738</v>
+      <c r="M62" s="32" t="n">
+        <v>-2411533564</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="inlineStr">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="C63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="26" t="n">
+      <c r="C63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="29" t="n">
         <v>2419176930</v>
       </c>
-      <c r="F63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="26" t="n">
+      <c r="F63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="29" t="n">
         <v>2419176930</v>
       </c>
-      <c r="H63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="26" t="n">
+      <c r="H63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="29" t="n">
         <v>2991439196</v>
       </c>
-      <c r="J63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="26" t="n">
+      <c r="J63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="29" t="n">
         <v>5410616126</v>
       </c>
-      <c r="L63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="26" t="n">
+      <c r="L63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="29" t="n">
+        <v>5410616126</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>6321</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Giá vốn hàng bán</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>2419176930</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>2419176930</v>
+      </c>
+      <c r="H64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="32" t="n">
         <v>2991439196</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>6321</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Giá vốn hàng bán</t>
-        </is>
-      </c>
-      <c r="C64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="29" t="n">
-        <v>2419176930</v>
-      </c>
-      <c r="F64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="29" t="n">
-        <v>2419176930</v>
-      </c>
-      <c r="H64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="29" t="n">
-        <v>2991439196</v>
-      </c>
-      <c r="J64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="29" t="n">
+      <c r="J64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="32" t="n">
         <v>5410616126</v>
       </c>
-      <c r="L64" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="29" t="n">
-        <v>2991439196</v>
+      <c r="L64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>5410616126</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="25" t="inlineStr">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>Chi phí tài chính</t>
         </is>
       </c>
-      <c r="C65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="26" t="n">
+      <c r="C65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="29" t="n">
         <v>60403</v>
       </c>
-      <c r="F65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="26" t="n">
+      <c r="F65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="29" t="n">
         <v>60403</v>
       </c>
-      <c r="H65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="26" t="n">
+      <c r="H65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="29" t="n">
         <v>15799</v>
       </c>
-      <c r="J65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="26" t="n">
+      <c r="J65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="29" t="n">
         <v>76202</v>
       </c>
-      <c r="L65" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="26" t="n">
+      <c r="L65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="29" t="n">
+        <v>76202</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Chi phí tài chính</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>60403</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>60403</v>
+      </c>
+      <c r="H66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="32" t="n">
         <v>15799</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Chi phí tài chính</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="29" t="n">
-        <v>60403</v>
-      </c>
-      <c r="F66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="29" t="n">
-        <v>60403</v>
-      </c>
-      <c r="H66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="29" t="n">
-        <v>15799</v>
-      </c>
-      <c r="J66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="29" t="n">
+      <c r="J66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="32" t="n">
         <v>76202</v>
       </c>
-      <c r="L66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="29" t="n">
-        <v>15799</v>
+      <c r="L66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>76202</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="25" t="inlineStr">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="C67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="26" t="n">
+      <c r="C67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="29" t="n">
         <v>6641156188</v>
       </c>
-      <c r="F67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="26" t="n">
+      <c r="F67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="29" t="n">
         <v>6641156188</v>
       </c>
-      <c r="H67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="26" t="n">
+      <c r="H67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="29" t="n">
         <v>6291816496</v>
       </c>
-      <c r="J67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="26" t="n">
+      <c r="J67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="29" t="n">
         <v>12932972684</v>
       </c>
-      <c r="L67" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="26" t="n">
-        <v>6291816496</v>
+      <c r="L67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="29" t="n">
+        <v>12932972684</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+      <c r="A68" s="31" t="inlineStr">
         <is>
           <t>6421</t>
         </is>
@@ -6219,42 +6168,42 @@
           <t>Chi phí nhân viên quản lý</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="29" t="n">
+      <c r="C68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="32" t="n">
         <v>5266634690</v>
       </c>
-      <c r="F68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="29" t="n">
+      <c r="F68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="32" t="n">
         <v>5266634690</v>
       </c>
-      <c r="H68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="29" t="n">
+      <c r="H68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="32" t="n">
         <v>4711018858</v>
       </c>
-      <c r="J68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="29" t="n">
+      <c r="J68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="32" t="n">
         <v>9977653548</v>
       </c>
-      <c r="L68" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="29" t="n">
-        <v>4711018858</v>
+      <c r="L68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>9977653548</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>6422</t>
         </is>
@@ -6264,42 +6213,42 @@
           <t>Chi phí vật liệu quản lý</t>
         </is>
       </c>
-      <c r="C69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="29" t="n">
+      <c r="C69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="32" t="n">
         <v>24621832</v>
       </c>
-      <c r="F69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="29" t="n">
+      <c r="F69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="32" t="n">
         <v>24621832</v>
       </c>
-      <c r="H69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="29" t="n">
+      <c r="H69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="32" t="n">
         <v>22152418</v>
       </c>
-      <c r="J69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="29" t="n">
+      <c r="J69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="32" t="n">
         <v>46774250</v>
       </c>
-      <c r="L69" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="29" t="n">
-        <v>22152418</v>
+      <c r="L69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>46774250</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>6424</t>
         </is>
@@ -6309,42 +6258,42 @@
           <t>Chi phí khấu hao TSCĐ</t>
         </is>
       </c>
-      <c r="C70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="29" t="n">
+      <c r="C70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="F70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="29" t="n">
+      <c r="F70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="H70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="29" t="n">
+      <c r="H70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="32" t="n">
         <v>5725755</v>
       </c>
-      <c r="J70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="29" t="n">
+      <c r="J70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="32" t="n">
         <v>11451510</v>
       </c>
-      <c r="L70" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="29" t="n">
-        <v>5725755</v>
+      <c r="L70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>11451510</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>6425</t>
         </is>
@@ -6354,42 +6303,42 @@
           <t>Thuế, phí và lệ phí</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="29" t="n">
+      <c r="C71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="32" t="n">
         <v>1800000</v>
       </c>
-      <c r="F71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="29" t="n">
+      <c r="F71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="32" t="n">
         <v>1800000</v>
       </c>
-      <c r="H71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="29" t="n">
+      <c r="H71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="32" t="n">
         <v>3601273</v>
       </c>
-      <c r="J71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="29" t="n">
+      <c r="J71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="32" t="n">
         <v>5401273</v>
       </c>
-      <c r="L71" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="29" t="n">
-        <v>3601273</v>
+      <c r="L71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5401273</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>6427</t>
         </is>
@@ -6399,42 +6348,42 @@
           <t>Chi phí dịch vụ mua ngoài</t>
         </is>
       </c>
-      <c r="C72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="29" t="n">
+      <c r="C72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="32" t="n">
         <v>113998029</v>
       </c>
-      <c r="F72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="29" t="n">
+      <c r="F72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="32" t="n">
         <v>113998029</v>
       </c>
-      <c r="H72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="29" t="n">
+      <c r="H72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="32" t="n">
         <v>110617187</v>
       </c>
-      <c r="J72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="29" t="n">
+      <c r="J72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="32" t="n">
         <v>224615216</v>
       </c>
-      <c r="L72" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="29" t="n">
-        <v>110617187</v>
+      <c r="L72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>224615216</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="28" t="inlineStr">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>6428</t>
         </is>
@@ -6444,128 +6393,128 @@
           <t>Chi phí bằng tiền khác</t>
         </is>
       </c>
-      <c r="C73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="29" t="n">
+      <c r="C73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="32" t="n">
         <v>1228375882</v>
       </c>
-      <c r="F73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="29" t="n">
+      <c r="F73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="32" t="n">
         <v>1228375882</v>
       </c>
-      <c r="H73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="29" t="n">
+      <c r="H73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="32" t="n">
         <v>1438701005</v>
       </c>
-      <c r="J73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="29" t="n">
+      <c r="J73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="32" t="n">
         <v>2667076887</v>
       </c>
-      <c r="L73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="29" t="n">
-        <v>1438701005</v>
+      <c r="L73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>2667076887</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="25" t="inlineStr">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>821</t>
         </is>
       </c>
-      <c r="B74" s="24" t="inlineStr">
+      <c r="B74" s="27" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp</t>
         </is>
       </c>
-      <c r="C74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="26" t="n">
+      <c r="C74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="29" t="n">
         <v>778687531</v>
       </c>
-      <c r="F74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="26" t="n">
+      <c r="F74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="29" t="n">
         <v>778687531</v>
       </c>
-      <c r="H74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="26" t="n">
+      <c r="H74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="29" t="n">
         <v>1086773307</v>
       </c>
-      <c r="J74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="26" t="n">
+      <c r="J74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="29" t="n">
         <v>1865460838</v>
       </c>
-      <c r="L74" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="26" t="n">
+      <c r="L74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="29" t="n">
+        <v>1865460838</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Chi phí thuế TNDN hiện hành</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>778687531</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>778687531</v>
+      </c>
+      <c r="H75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="32" t="n">
         <v>1086773307</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>8211</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>Chi phí thuế TNDN hiện hành</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="29" t="n">
-        <v>778687531</v>
-      </c>
-      <c r="F75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="29" t="n">
-        <v>778687531</v>
-      </c>
-      <c r="H75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="29" t="n">
-        <v>1086773307</v>
-      </c>
-      <c r="J75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="29" t="n">
+      <c r="J75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="32" t="n">
         <v>1865460838</v>
       </c>
-      <c r="L75" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="29" t="n">
-        <v>1086773307</v>
+      <c r="L75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>1865460838</v>
       </c>
     </row>
   </sheetData>
